--- a/data/trans_orig/P78C_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023</t>
+          <t>Población según la categoría profesional que tiene o tenía en la empresa donde trabaja o trabajaba la persona sustentadora principal en 2023 (tasa de respuesta: 98,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113596</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146405</t>
+          <t>145868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86572</t>
+          <t>87370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106734</t>
+          <t>106330</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209453</t>
+          <t>209134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>247895</t>
+          <t>248942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2628</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2628</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1295,97 +1295,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3976</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2628</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26998</t>
+          <t>26295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14932</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48899</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302182</t>
+          <t>300865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342395</t>
+          <t>339555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201048</t>
+          <t>194841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>405550</t>
+          <t>406432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>489197</t>
+          <t>484078</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>728190</t>
+          <t>729076</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39827</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52885</t>
+          <t>53173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>13959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>24979</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>234442</t>
+          <t>243252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>17728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279241</t>
+          <t>290477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>23223</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49384</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33274</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>39200</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75946</t>
+          <t>74230</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356013</t>
+          <t>355870</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>398372</t>
+          <t>399536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>401000</t>
+          <t>399711</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>428348</t>
+          <t>427504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>768360</t>
+          <t>767947</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819978</t>
+          <t>819222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67252</t>
+          <t>66231</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31040</t>
+          <t>30799</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59529</t>
+          <t>59030</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>91464</t>
+          <t>89584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,62 +2807,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>8137</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>8234</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32993</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>21520</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,47 +3126,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7459</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7596</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48804</t>
+          <t>48977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80105</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34479</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>54082</t>
+          <t>53291</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88342</t>
+          <t>88070</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>125830</t>
+          <t>126357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>193366</t>
+          <t>182096</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>628243</t>
+          <t>628487</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>475756</t>
+          <t>473339</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>514513</t>
+          <t>514595</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>550376</t>
+          <t>544555</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1129838</t>
+          <t>1131864</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,49%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>66135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41972</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93691</t>
+          <t>93478</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>581234</t>
+          <t>598146</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>13810</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>747084</t>
+          <t>753841</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>42824</t>
+          <t>43726</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>16544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54237</t>
+          <t>52666</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15975</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>23002</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>37877</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131256</t>
+          <t>130027</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>55478</t>
+          <t>56022</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>83718</t>
+          <t>83807</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>96274</t>
+          <t>89991</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>199356</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>367476</t>
+          <t>370951</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>409351</t>
+          <t>409920</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>326740</t>
+          <t>325066</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>353129</t>
+          <t>351512</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>707424</t>
+          <t>708195</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>755269</t>
+          <t>754326</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>53463</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>47201</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>71943</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,47 +4603,47 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>5104</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>10678</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21957</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>31755</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>53751</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>66185</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>99272</t>
+          <t>98628</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>44292</t>
+          <t>44908</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>66513</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>120192</t>
+          <t>119390</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>157808</t>
+          <t>156398</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>226644</t>
+          <t>228048</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>255553</t>
+          <t>257094</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>369721</t>
+          <t>370724</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>458187</t>
+          <t>457102</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>597480</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>765241</t>
+          <t>754442</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>52828</t>
+          <t>50571</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>68848</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>12793</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>9270</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11946</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>41552</t>
+          <t>41366</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>62424</t>
+          <t>62944</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>15985</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>81348</t>
+          <t>79662</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>43062</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>131842</t>
+          <t>133478</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>163195</t>
+          <t>164363</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>188770</t>
+          <t>189704</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>151728</t>
+          <t>150945</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>168929</t>
+          <t>168851</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>321395</t>
+          <t>321028</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>353572</t>
+          <t>352262</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,24%</t>
         </is>
       </c>
     </row>
@@ -6291,12 +6291,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>44935</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>52887</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>5540</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6517,12 +6517,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9028</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13465</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>10839</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -6743,12 +6743,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>306</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>35849</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>55580</t>
+          <t>54886</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>28456</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>43794</t>
+          <t>43941</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>68869</t>
+          <t>69736</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>93275</t>
+          <t>94141</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1649369</t>
+          <t>1596478</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2276213</t>
+          <t>2276360</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2104567</t>
+          <t>2075468</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2371668</t>
+          <t>2364798</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3716044</t>
+          <t>3782930</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4604112</t>
+          <t>4591892</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>191004</t>
+          <t>185726</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>278556</t>
+          <t>281936</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73254</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>113447</t>
+          <t>114745</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>281965</t>
+          <t>280631</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>382568</t>
+          <t>380516</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -7312,12 +7312,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>25435</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7425,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>829649</t>
+          <t>953297</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25922</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>1232232</t>
+          <t>1061249</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -7538,12 +7538,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>86837</t>
+          <t>87237</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139646</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>56850</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>403699</t>
+          <t>403294</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>167127</t>
+          <t>170672</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>494460</t>
+          <t>553903</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -7651,12 +7651,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>26318</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>21807</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>40507</t>
+          <t>40674</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>72128</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -7764,12 +7764,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>291968</t>
+          <t>280547</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>425847</t>
+          <t>425486</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>228037</t>
+          <t>220202</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>326012</t>
+          <t>324946</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7814,12 +7814,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>551896</t>
+          <t>568641</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>725653</t>
+          <t>727485</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78C_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78C_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>134268</t>
+          <t>149935</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>114503</t>
+          <t>132102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145868</t>
+          <t>161972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>115496</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87370</t>
+          <t>101361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106330</t>
+          <t>124913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>232297</t>
+          <t>265431</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>209134</t>
+          <t>244072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248942</t>
+          <t>280423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,41%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>24044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33446</t>
+          <t>26834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15777</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27641</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1516,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>157757</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157757</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157757</t>
+          <t>173606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>136564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>136564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>136564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>310170</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>310170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>310170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>323122</t>
+          <t>364571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>300865</t>
+          <t>339621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339555</t>
+          <t>383973</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>339680</t>
+          <t>379770</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194841</t>
+          <t>363915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406432</t>
+          <t>391457</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>662802</t>
+          <t>744341</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>484078</t>
+          <t>715405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>729076</t>
+          <t>769673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>42725</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53173</t>
+          <t>59939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6080</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>20511</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>20228</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>75335</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243252</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>88072</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290477</t>
+          <t>35298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>13705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>25584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49384</t>
+          <t>53393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>40018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39200</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74230</t>
+          <t>85649</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -2424,17 +2424,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>402776</t>
+          <t>453415</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>402776</t>
+          <t>453415</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>402776</t>
+          <t>453415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>453489</t>
+          <t>434050</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>453489</t>
+          <t>434050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>453489</t>
+          <t>434050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>856265</t>
+          <t>887465</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>856265</t>
+          <t>887465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>856265</t>
+          <t>887465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>378092</t>
+          <t>442771</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>355870</t>
+          <t>416803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>399536</t>
+          <t>465554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>414456</t>
+          <t>469470</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>399711</t>
+          <t>452984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>427504</t>
+          <t>483670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>792549</t>
+          <t>912241</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>767947</t>
+          <t>882873</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>819222</t>
+          <t>940789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>57653</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66231</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>35134</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>73660</t>
+          <t>83279</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>68219</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>89584</t>
+          <t>101776</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>35249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>37784</t>
+          <t>40792</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>30726</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50368</t>
+          <t>53870</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3106,102 +3106,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>20015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9697</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>13626</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>24248</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7459</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>11862</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>6009</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>21494</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>62909</t>
+          <t>71198</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>48977</t>
+          <t>55513</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79278</t>
+          <t>89493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>49271</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>61882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>105955</t>
+          <t>120470</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>126357</t>
+          <t>141322</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>529866</t>
+          <t>611646</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>529866</t>
+          <t>611646</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>529866</t>
+          <t>611646</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>502561</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>502561</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>502561</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1032428</t>
+          <t>1182409</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1032428</t>
+          <t>1182409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1032428</t>
+          <t>1182409</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>442144</t>
+          <t>477627</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182096</t>
+          <t>456568</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>628487</t>
+          <t>503051</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>491962</t>
+          <t>494303</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>473339</t>
+          <t>478464</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>514595</t>
+          <t>512276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>934106</t>
+          <t>971930</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>544555</t>
+          <t>942883</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1131864</t>
+          <t>1002565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,63%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66135</t>
+          <t>62786</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>31562</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>40903</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>70329</t>
+          <t>79414</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>63605</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>93478</t>
+          <t>96925</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>251983</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>598146</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>258743</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>9587</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>753841</t>
+          <t>24614</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3901,32 +3901,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43726</t>
+          <t>39918</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3936,32 +3936,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>11544</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3971,32 +3971,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>38595</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>54643</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -4014,32 +4014,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4049,32 +4049,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6896</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4084,32 +4084,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>87748</t>
+          <t>95772</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38376</t>
+          <t>77671</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>130027</t>
+          <t>114232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>79036</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>56022</t>
+          <t>65698</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>91905</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>157993</t>
+          <t>174808</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>89991</t>
+          <t>152724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>199356</t>
+          <t>200649</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -4240,17 +4240,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>864458</t>
+          <t>675413</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>864458</t>
+          <t>675413</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>864458</t>
+          <t>675413</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>615257</t>
+          <t>632851</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>615257</t>
+          <t>632851</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>615257</t>
+          <t>632851</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1479716</t>
+          <t>1308264</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1479716</t>
+          <t>1308264</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1479716</t>
+          <t>1308264</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>390530</t>
+          <t>418191</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>370951</t>
+          <t>396215</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>409920</t>
+          <t>440381</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>340999</t>
+          <t>379498</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>325066</t>
+          <t>364511</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>351512</t>
+          <t>392279</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>731530</t>
+          <t>797689</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>708195</t>
+          <t>769745</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>754326</t>
+          <t>821738</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,7%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30211</t>
+          <t>31939</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53463</t>
+          <t>55830</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>15450</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>65036</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>71943</t>
+          <t>80672</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8547</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4696,32 +4696,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>13818</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -4809,32 +4809,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17775</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>38750</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4844,32 +4844,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4879,32 +4879,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>40387</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>31755</t>
+          <t>33276</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>53751</t>
+          <t>55454</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4922,32 +4922,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4957,22 +4957,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>562</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4992,32 +4992,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>9718</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>16658</t>
+          <t>16659</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5035,32 +5035,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>81287</t>
+          <t>94172</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>65400</t>
+          <t>78524</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>98628</t>
+          <t>113137</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>61552</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>44908</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>72459</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>155724</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>137053</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>156398</t>
+          <t>180048</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -5148,17 +5148,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553160</t>
+          <t>600973</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553160</t>
+          <t>600973</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553160</t>
+          <t>600973</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>434707</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>434707</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>434707</t>
+          <t>484573</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>987868</t>
+          <t>1085546</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>987868</t>
+          <t>1085546</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>987868</t>
+          <t>1085546</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5265,32 +5265,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>242220</t>
+          <t>266439</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>228048</t>
+          <t>248345</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>257094</t>
+          <t>280774</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>420086</t>
+          <t>236071</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>370724</t>
+          <t>225743</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>457102</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>662305</t>
+          <t>502509</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>597480</t>
+          <t>483474</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>754442</t>
+          <t>520436</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>74,0%</t>
         </is>
       </c>
     </row>
@@ -5378,32 +5378,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>35456</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>50571</t>
+          <t>57060</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>47628</t>
+          <t>53140</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>41783</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>67575</t>
+          <t>65620</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -5491,32 +5491,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5526,32 +5526,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1449</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>436</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5561,32 +5561,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5604,32 +5604,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5639,32 +5639,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5674,32 +5674,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5717,32 +5717,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>16185</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>10862</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>23946</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5752,32 +5752,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>11330</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5787,32 +5787,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5830,32 +5830,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5900,32 +5900,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -5943,32 +5943,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>57755</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>41366</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>70708</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>43143</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>38518</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>79662</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>95123</t>
+          <t>104815</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>48554</t>
+          <t>90786</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>133478</t>
+          <t>119853</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -6056,17 +6056,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>362966</t>
+          <t>401627</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>362966</t>
+          <t>401627</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>362966</t>
+          <t>401627</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>479092</t>
+          <t>301672</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>479092</t>
+          <t>301672</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>479092</t>
+          <t>301672</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>842057</t>
+          <t>703299</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>842057</t>
+          <t>703299</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>842057</t>
+          <t>703299</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6173,32 +6173,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>176779</t>
+          <t>194650</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>164363</t>
+          <t>180906</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>189704</t>
+          <t>209711</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>160869</t>
+          <t>175665</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>150945</t>
+          <t>164387</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>168851</t>
+          <t>186087</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>337647</t>
+          <t>370316</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>321028</t>
+          <t>352782</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>352262</t>
+          <t>386358</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -6286,32 +6286,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>36057</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>48739</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6321,32 +6321,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6356,32 +6356,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>45944</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>36445</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6409,84 +6409,84 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4621</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>2339</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>6363</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6512,32 +6512,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -6625,32 +6625,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>17371</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6660,32 +6660,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -6738,32 +6738,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6773,32 +6773,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>299</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6808,32 +6808,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7857</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6851,32 +6851,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>47705</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>54886</t>
+          <t>57931</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6886,32 +6886,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>35891</t>
+          <t>38999</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>31550</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>43941</t>
+          <t>48586</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6921,32 +6921,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>81019</t>
+          <t>86704</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>73477</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>94141</t>
+          <t>99827</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -6964,17 +6964,17 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>280884</t>
+          <t>308120</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>280884</t>
+          <t>308120</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>280884</t>
+          <t>308120</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>213560</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>213560</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>213560</t>
+          <t>234513</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>494444</t>
+          <t>542633</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>494444</t>
+          <t>542633</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>494444</t>
+          <t>542633</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7081,32 +7081,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2087155</t>
+          <t>2314184</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>1596478</t>
+          <t>2262136</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2276360</t>
+          <t>2367283</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7116,32 +7116,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2266081</t>
+          <t>2250273</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2075468</t>
+          <t>2211681</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2364798</t>
+          <t>2283320</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7151,32 +7151,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>4353236</t>
+          <t>4564456</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3782930</t>
+          <t>4498822</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4591892</t>
+          <t>4621627</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -7194,32 +7194,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>243015</t>
+          <t>268604</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>185726</t>
+          <t>237883</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>281936</t>
+          <t>301205</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7229,32 +7229,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>109329</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>73254</t>
+          <t>93373</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>114745</t>
+          <t>129443</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7264,32 +7264,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>338702</t>
+          <t>377932</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>280631</t>
+          <t>345437</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>380516</t>
+          <t>417398</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -7307,32 +7307,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26436</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7342,32 +7342,32 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7377,32 +7377,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>32755</t>
+          <t>35487</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -7420,32 +7420,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>273758</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>28073</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>953297</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7455,32 +7455,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>25922</t>
+          <t>29786</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7490,32 +7490,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>291017</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>1061249</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7533,32 +7533,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>116824</t>
+          <t>125967</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>87237</t>
+          <t>106109</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>139646</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7568,32 +7568,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>130947</t>
+          <t>68989</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>56850</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>403294</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7603,32 +7603,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>247772</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>170672</t>
+          <t>171611</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>553903</t>
+          <t>223804</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7646,69 +7646,69 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>47891</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>54130</t>
+          <t>64960</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>10699</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>24367</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>14241</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>21890</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
           <t>71</t>
@@ -7716,32 +7716,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>64641</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>40674</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>84221</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7759,32 +7759,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>375339</t>
+          <t>417058</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>280547</t>
+          <t>381091</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>425486</t>
+          <t>458619</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7794,32 +7794,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>285105</t>
+          <t>321723</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>220202</t>
+          <t>294697</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>324946</t>
+          <t>351378</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7829,32 +7829,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>660444</t>
+          <t>738781</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>568641</t>
+          <t>691417</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>727485</t>
+          <t>785232</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -7872,17 +7872,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3151867</t>
+          <t>3224800</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2815243</t>
+          <t>2794987</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7942,17 +7942,17 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>5967110</t>
+          <t>6019786</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
